--- a/model_comparison.xlsx
+++ b/model_comparison.xlsx
@@ -435,7 +435,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7542372881355932</v>
+        <v>0.7559322033898305</v>
       </c>
     </row>
     <row r="3">

--- a/model_comparison.xlsx
+++ b/model_comparison.xlsx
@@ -435,7 +435,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7559322033898305</v>
+        <v>0.7542372881355932</v>
       </c>
     </row>
     <row r="3">

--- a/model_comparison.xlsx
+++ b/model_comparison.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Decision Tree</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -448,6 +448,16 @@
         <v>0.8</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Logistic Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.7542372881355932</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
